--- a/artfynd/A 35911-2021 artfynd.xlsx
+++ b/artfynd/A 35911-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35911-2021 artfynd.xlsx
+++ b/artfynd/A 35911-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>77500161</v>
+        <v>133472367</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Labbokilen, Upl</t>
+          <t>Labbo, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673569.3971941608</v>
+        <v>673563</v>
       </c>
       <c r="R2" t="n">
-        <v>6698917.221153461</v>
+        <v>6698828</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,24 +764,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -806,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77500171</v>
+        <v>133472371</v>
       </c>
       <c r="B3" t="n">
-        <v>77882</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,40 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6431</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Labbokilen, Upl</t>
+          <t>Labbo, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673569.3971941608</v>
+        <v>673597</v>
       </c>
       <c r="R3" t="n">
-        <v>6698917.221153461</v>
+        <v>6698826</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,24 +871,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -937,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>77500162</v>
+        <v>77500171</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,27 +900,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6431</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -981,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673569.3971941608</v>
+        <v>673569</v>
       </c>
       <c r="R4" t="n">
-        <v>6698917.221153461</v>
+        <v>6698917</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1014,19 +960,9 @@
           <t>2019-05-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-05-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,6 +974,21 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1057,12 +1008,7 @@
         <v>84100504</v>
       </c>
       <c r="B5" t="n">
-        <v>77882</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>673556.5137005101</v>
+        <v>673557</v>
       </c>
       <c r="R5" t="n">
-        <v>6698885.908753394</v>
+        <v>6698886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,19 +1073,9 @@
           <t>2020-03-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-03-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,12 +1120,7 @@
         <v>84100524</v>
       </c>
       <c r="B6" t="n">
-        <v>77882</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>673564.9958909457</v>
+        <v>673565</v>
       </c>
       <c r="R6" t="n">
-        <v>6698884.829228831</v>
+        <v>6698885</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,19 +1185,9 @@
           <t>2020-03-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-03-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,61 +1229,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84100505</v>
+        <v>77500161</v>
       </c>
       <c r="B7" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Labbo, Upl</t>
+          <t>Labbokilen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>673526.6322761216</v>
+        <v>673569</v>
       </c>
       <c r="R7" t="n">
-        <v>6698930.028302585</v>
+        <v>6698917</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,22 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-03-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-03-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,6 +1314,21 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1432,12 +1348,7 @@
         <v>84100506</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>673560.1588906923</v>
+        <v>673560</v>
       </c>
       <c r="R8" t="n">
-        <v>6698934.107499034</v>
+        <v>6698934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,19 +1413,9 @@
           <t>2020-03-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-03-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,37 +1457,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84100522</v>
+        <v>84100520</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1596,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673563.4184899802</v>
+        <v>673565</v>
       </c>
       <c r="R9" t="n">
-        <v>6698876.337056346</v>
+        <v>6698893</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,21 +1525,11 @@
           <t>2020-03-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-03-24</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1652,6 +1538,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1668,15 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84100520</v>
+        <v>133472366</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673565.0889398042</v>
+        <v>673571</v>
       </c>
       <c r="R10" t="n">
-        <v>6698893.250371668</v>
+        <v>6698867</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1738,22 +1634,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-03-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-03-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,21 +1660,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1795,15 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99325456</v>
+        <v>99340757</v>
       </c>
       <c r="B11" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,21 +1687,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1833,16 +1709,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>FM-19257-5-49, Upl</t>
+          <t>FM-240-1-41, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673441.2888445137</v>
+        <v>673408</v>
       </c>
       <c r="R11" t="n">
-        <v>6698765.038701381</v>
+        <v>6698770</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1869,22 +1750,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2007-06-13</t>
+          <t>2020-04-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>04:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2007-06-13</t>
+          <t>2020-04-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>04:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,15 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99340993</v>
+        <v>99340992</v>
       </c>
       <c r="B12" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673490.3993137887</v>
+        <v>673491</v>
       </c>
       <c r="R12" t="n">
-        <v>6698899.579956017</v>
+        <v>6698900</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1994,7 +1870,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-04-17</t>
+          <t>2020-04-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2004,7 +1880,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-04-17</t>
+          <t>2020-04-19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2043,12 +1919,7 @@
         <v>99341102</v>
       </c>
       <c r="B13" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2089,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673481.3365629147</v>
+        <v>673482</v>
       </c>
       <c r="R13" t="n">
-        <v>6698829.832375406</v>
+        <v>6698830</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2165,45 +2036,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133472361</v>
+        <v>119796729</v>
       </c>
       <c r="B14" t="n">
-        <v>102303</v>
+        <v>58812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>100119</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Camerano, 1882)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Labbo, Upl</t>
+          <t>Kärnkraftverk, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>673630</v>
+        <v>673658</v>
       </c>
       <c r="R14" t="n">
-        <v>6698845</v>
+        <v>6698790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2230,22 +2105,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2260,22 +2130,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133472367</v>
+        <v>89718904</v>
       </c>
       <c r="B15" t="n">
-        <v>92632</v>
+        <v>4781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,21 +2153,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2307,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673563</v>
+        <v>673406</v>
       </c>
       <c r="R15" t="n">
-        <v>6698828</v>
+        <v>6698791</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2337,22 +2207,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2020-12-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2020-12-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,48 +2239,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133472363</v>
+        <v>99340758</v>
       </c>
       <c r="B16" t="n">
-        <v>58260</v>
+        <v>58039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103012</v>
+        <v>102626</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Labbo, Upl</t>
+          <t>FM-240-1-41, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>673620</v>
+        <v>673408</v>
       </c>
       <c r="R16" t="n">
-        <v>6698871</v>
+        <v>6698770</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2444,22 +2308,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2474,22 +2338,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133472370</v>
+        <v>99340994</v>
       </c>
       <c r="B17" t="n">
-        <v>104692</v>
+        <v>58039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,37 +2365,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>102626</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Labbo, Upl</t>
+          <t>FM-234-3-62, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>673587</v>
+        <v>673491</v>
       </c>
       <c r="R17" t="n">
-        <v>6698827</v>
+        <v>6698900</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2551,22 +2423,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2581,22 +2453,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133472369</v>
+        <v>99341104</v>
       </c>
       <c r="B18" t="n">
-        <v>102303</v>
+        <v>58039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,37 +2480,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221235</v>
+        <v>102626</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Labbo, Upl</t>
+          <t>FM-232-1-66, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>673582</v>
+        <v>673482</v>
       </c>
       <c r="R18" t="n">
-        <v>6698824</v>
+        <v>6698830</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2658,22 +2538,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2688,22 +2568,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133472364</v>
+        <v>99369305</v>
       </c>
       <c r="B19" t="n">
-        <v>101388</v>
+        <v>58039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,37 +2595,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>102626</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Labbo, Upl</t>
+          <t>FM-9140-4-64, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>673579</v>
+        <v>673428</v>
       </c>
       <c r="R19" t="n">
-        <v>6698849</v>
+        <v>6698764</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2763,24 +2656,25 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2795,60 +2689,68 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133472366</v>
+        <v>99343224</v>
       </c>
       <c r="B20" t="n">
-        <v>80474</v>
+        <v>58463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>102995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Labbo, Upl</t>
+          <t>FM-320-5-14, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>673571</v>
+        <v>673445</v>
       </c>
       <c r="R20" t="n">
-        <v>6698867</v>
+        <v>6698942</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2872,22 +2774,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,60 +2804,68 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133472372</v>
+        <v>99369310</v>
       </c>
       <c r="B21" t="n">
-        <v>102303</v>
+        <v>58393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>102999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Labbo, Upl</t>
+          <t>FM-9140-4-64, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>673600</v>
+        <v>673428</v>
       </c>
       <c r="R21" t="n">
-        <v>6698818</v>
+        <v>6698764</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2977,24 +2887,25 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2002-06-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2002-06-12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,15 +2920,1787 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133472363</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58260</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>673620</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6698871</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>84100515</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>673567</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6698933</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-03-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-03-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>84100517</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>673541</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6698901</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-03-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-03-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>89718903</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>673410</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6698791</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>89718895</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>673431</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6698759</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>99325456</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>FM-19257-5-49, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>673441</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6698765</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2007-06-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2007-06-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133472368</v>
+      </c>
+      <c r="B28" t="n">
+        <v>104880</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220460</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tandrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cardamine bulbifera</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>673584</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6698834</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133472361</v>
+      </c>
+      <c r="B29" t="n">
+        <v>102318</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>673630</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6698845</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133472369</v>
+      </c>
+      <c r="B30" t="n">
+        <v>102318</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>673582</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6698824</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133472372</v>
+      </c>
+      <c r="B31" t="n">
+        <v>102318</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>673600</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6698818</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>84100505</v>
+      </c>
+      <c r="B32" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>673527</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6698930</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-03-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-03-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133472370</v>
+      </c>
+      <c r="B33" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>673587</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6698827</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>77500162</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Labbokilen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>673569</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6698917</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>84100522</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>673563</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6698876</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2020-03-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2020-03-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>89718901</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>673404</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6698789</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133472364</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Labbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>673579</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6698849</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>112649234</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gunnarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>673407</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6698791</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>ev. gyllenfingersvamp</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
